--- a/AdvanceExcel/Scenrio Manager.xlsx
+++ b/AdvanceExcel/Scenrio Manager.xlsx
@@ -1,45 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Practice\For Golu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79040C2D-3E7B-4D2A-928C-5DF6A58663BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB978019-40F9-4F8E-8AC2-10AA8AB3C9C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="4" xr2:uid="{DFFBC060-66F1-4E5C-BD70-1A334413188F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="2" activeTab="6" xr2:uid="{DFFBC060-66F1-4E5C-BD70-1A334413188F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Scenario Summary Sheet3" sheetId="5" r:id="rId1"/>
-    <sheet name="Scenario Summary Sheet1" sheetId="6" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Scenario Summary Sheet1" sheetId="6" r:id="rId1"/>
+    <sheet name="Scenario Summary Sheet2" sheetId="9" r:id="rId2"/>
+    <sheet name="Scenario Summary Sheet3" sheetId="5" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
-    <sheet name="Scenario Summary" sheetId="9" r:id="rId5"/>
-    <sheet name="Sheet2" sheetId="7" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId6"/>
+    <sheet name="Scenario Summary" sheetId="15" r:id="rId7"/>
+    <sheet name="Sheet4" sheetId="10" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="Accomodation">Sheet3!$B$8</definedName>
     <definedName name="Ad_Spend">Sheet2!$B$2</definedName>
     <definedName name="Budget">Sheet3!$B$4</definedName>
     <definedName name="Conversion_Rate_Percentages">Sheet2!$B$4</definedName>
+    <definedName name="Cost_Growth">Sheet4!$C$7</definedName>
     <definedName name="Fixed_Cost">Sheet1!$B$5</definedName>
     <definedName name="Food">Sheet3!$B$9</definedName>
+    <definedName name="Interest_Rate">Sheet4!$C$6</definedName>
     <definedName name="Leads_Generated">Sheet2!$B$3</definedName>
     <definedName name="Mis">Sheet3!$B$11</definedName>
+    <definedName name="Price_Growth">Sheet4!$C$8</definedName>
     <definedName name="Profit_Formula">Sheet1!$B$6</definedName>
     <definedName name="Revenue">Sheet2!$B$6</definedName>
     <definedName name="Revenue_per_Sale">Sheet2!$B$5</definedName>
     <definedName name="ROI_Percentages">Sheet2!$B$7</definedName>
+    <definedName name="Sales_Growth">Sheet4!$C$3</definedName>
     <definedName name="Sales_Price____Unit">Sheet1!$B$2</definedName>
     <definedName name="Spare_Cash">Sheet3!$B$14</definedName>
+    <definedName name="Tax_Rate">Sheet4!$C$1</definedName>
     <definedName name="Tickets">Sheet3!$B$10</definedName>
     <definedName name="Total_Expense">Sheet3!$B$13</definedName>
     <definedName name="Train_Travel">Sheet3!$B$7</definedName>
     <definedName name="Unit_Sold">Sheet1!$B$3</definedName>
     <definedName name="Variable_Cost___Unit">Sheet1!$B$4</definedName>
+    <definedName name="Year_1_Cost">Sheet4!$C$5</definedName>
+    <definedName name="Year_1_Price">Sheet4!$C$4</definedName>
+    <definedName name="Year_1_Sales">Sheet4!$C$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
   <si>
     <t>Sales Price  / Unit</t>
   </si>
@@ -249,12 +259,105 @@
   <si>
     <t>Created by Triveni on 10-02-2026
 Modified by Triveni on 10-02-2026</t>
+  </si>
+  <si>
+    <t>Tax Rate</t>
+  </si>
+  <si>
+    <t>Year 1 Sales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales Growth </t>
+  </si>
+  <si>
+    <t>Year 1 Price</t>
+  </si>
+  <si>
+    <t>Year 1 Cost</t>
+  </si>
+  <si>
+    <t>Cost Growth</t>
+  </si>
+  <si>
+    <t>Price Growth</t>
+  </si>
+  <si>
+    <t>Interest Rate</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Unit Sales</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Unit Cost</t>
+  </si>
+  <si>
+    <t>Costs</t>
+  </si>
+  <si>
+    <t>Before Tax Profit</t>
+  </si>
+  <si>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>After Tax Profit</t>
+  </si>
+  <si>
+    <t>Year_1_Sales</t>
+  </si>
+  <si>
+    <t>Sales_Growth</t>
+  </si>
+  <si>
+    <t>Year_1_Price</t>
+  </si>
+  <si>
+    <t>Best</t>
+  </si>
+  <si>
+    <t>Created by Triveni on 29-03-2026</t>
+  </si>
+  <si>
+    <t>Worst</t>
+  </si>
+  <si>
+    <t>NPV</t>
+  </si>
+  <si>
+    <t>$C$20</t>
+  </si>
+  <si>
+    <t>Most Probably</t>
+  </si>
+  <si>
+    <t>$C$18</t>
+  </si>
+  <si>
+    <t>$D$18</t>
+  </si>
+  <si>
+    <t>$E$18</t>
+  </si>
+  <si>
+    <t>$F$18</t>
+  </si>
+  <si>
+    <t>$G$18</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="8" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ \-#,##0.00"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -310,7 +413,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -333,6 +436,12 @@
       <patternFill patternType="solid">
         <fgColor indexed="22"/>
         <bgColor indexed="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -401,7 +510,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -433,7 +542,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -446,17 +554,40 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -790,6 +921,335 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E9AE4D0-0C5B-472E-99DF-84FAE0CEC631}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="B1:G14"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12.6640625" bestFit="1" customWidth="1" outlineLevel="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+    </row>
+    <row r="3" spans="2:7" ht="15.6" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="21.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="E4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="9"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="8"/>
+      <c r="C6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>500</v>
+      </c>
+      <c r="E6" s="12">
+        <v>500</v>
+      </c>
+      <c r="F6" s="12">
+        <v>620</v>
+      </c>
+      <c r="G6" s="12">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="8"/>
+      <c r="C7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7" s="12">
+        <v>100</v>
+      </c>
+      <c r="F7" s="12">
+        <v>250</v>
+      </c>
+      <c r="G7" s="12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="8"/>
+      <c r="C8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8">
+        <v>300</v>
+      </c>
+      <c r="E8" s="12">
+        <v>300</v>
+      </c>
+      <c r="F8" s="12">
+        <v>250</v>
+      </c>
+      <c r="G8" s="12">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="8"/>
+      <c r="C9" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9">
+        <v>10000</v>
+      </c>
+      <c r="E9" s="12">
+        <v>10000</v>
+      </c>
+      <c r="F9" s="12">
+        <v>10000</v>
+      </c>
+      <c r="G9" s="12">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="2:7" ht="15" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="4">
+        <v>10000</v>
+      </c>
+      <c r="E11" s="4">
+        <v>10000</v>
+      </c>
+      <c r="F11" s="4">
+        <v>82500</v>
+      </c>
+      <c r="G11" s="4">
+        <v>-5500</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89FEEC00-1B29-48B2-A252-2F127EEBDA47}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="B2:G12"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25.77734375" customWidth="1"/>
+    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="12.6640625" bestFit="1" customWidth="1" outlineLevel="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B2" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+    </row>
+    <row r="3" spans="2:7" ht="15.6" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="43.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="2">
+        <v>200000</v>
+      </c>
+      <c r="E6" s="21">
+        <v>200000</v>
+      </c>
+      <c r="F6" s="21">
+        <v>3000000</v>
+      </c>
+      <c r="G6" s="21">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E7" s="21">
+        <v>1000</v>
+      </c>
+      <c r="F7" s="21">
+        <v>1500</v>
+      </c>
+      <c r="G7" s="21">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+    </row>
+    <row r="9" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E9" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="F9" s="2">
+        <v>-0.75</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="22" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B11" s="22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B27682-AF73-45EC-B32A-062CD306D081}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
@@ -989,189 +1449,288 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E9AE4D0-0C5B-472E-99DF-84FAE0CEC631}">
-  <sheetPr>
-    <outlinePr summaryBelow="0"/>
-  </sheetPr>
-  <dimension ref="B1:G14"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D98FD759-83AD-4973-A6D0-DC90F1A1042F}">
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="12.6640625" bestFit="1" customWidth="1" outlineLevel="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-    </row>
-    <row r="3" spans="2:7" ht="15.6" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="11" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="21.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="E4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-    </row>
-    <row r="6" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="8"/>
-      <c r="C6" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2">
         <v>500</v>
       </c>
-      <c r="E6" s="12">
+      <c r="D2" s="2">
+        <v>620</v>
+      </c>
+      <c r="E2" s="2">
+        <v>400</v>
+      </c>
+      <c r="F2" s="2">
         <v>500</v>
       </c>
-      <c r="F6" s="12">
-        <v>620</v>
-      </c>
-      <c r="G6" s="12">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="8"/>
-      <c r="C7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
         <v>100</v>
       </c>
-      <c r="E7" s="12">
+      <c r="D3" s="2">
+        <v>250</v>
+      </c>
+      <c r="E3" s="2">
+        <v>90</v>
+      </c>
+      <c r="F3" s="2">
         <v>100</v>
       </c>
-      <c r="F7" s="12">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2">
+        <v>300</v>
+      </c>
+      <c r="D4" s="2">
         <v>250</v>
       </c>
-      <c r="G7" s="12">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="8"/>
-      <c r="C8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8">
+      <c r="E4" s="2">
+        <v>350</v>
+      </c>
+      <c r="F4" s="2">
         <v>300</v>
       </c>
-      <c r="E8" s="12">
-        <v>300</v>
-      </c>
-      <c r="F8" s="12">
-        <v>250</v>
-      </c>
-      <c r="G8" s="12">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="8"/>
-      <c r="C9" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2">
         <v>10000</v>
       </c>
-      <c r="E9" s="12">
+      <c r="D5" s="2">
         <v>10000</v>
       </c>
-      <c r="F9" s="12">
+      <c r="E5" s="2">
         <v>10000</v>
       </c>
-      <c r="G9" s="12">
+      <c r="F5" s="2">
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B10" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="9"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-    </row>
-    <row r="11" spans="2:7" ht="15" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="14"/>
-      <c r="C11" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="4">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <f>(B2*B3)-(B4*B3+B5)</f>
         <v>10000</v>
       </c>
-      <c r="E11" s="4">
-        <v>10000</v>
-      </c>
-      <c r="F11" s="4">
-        <v>82500</v>
-      </c>
-      <c r="G11" s="4">
-        <v>-5500</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
-        <v>14</v>
-      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
     </row>
   </sheetData>
+  <scenarios current="0" sqref="B6">
+    <scenario name="Expected" locked="1" count="4" user="Triveni" comment="Created by Triveni on 09-02-2026">
+      <inputCells r="B2" val="500"/>
+      <inputCells r="B3" val="100"/>
+      <inputCells r="B4" val="300"/>
+      <inputCells r="B5" val="10000"/>
+    </scenario>
+    <scenario name="Best_Case" locked="1" count="4" user="Triveni" comment="Created by Triveni on 09-02-2026">
+      <inputCells r="B2" val="620"/>
+      <inputCells r="B3" val="250"/>
+      <inputCells r="B4" val="250"/>
+      <inputCells r="B5" val="10000"/>
+    </scenario>
+    <scenario name="Worst_Case" locked="1" count="4" user="Triveni" comment="Created by Triveni on 09-02-2026">
+      <inputCells r="B2" val="400"/>
+      <inputCells r="B3" val="90"/>
+      <inputCells r="B4" val="350"/>
+      <inputCells r="B5" val="10000"/>
+    </scenario>
+  </scenarios>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24145780-E5EB-4577-878A-05C93A422FE5}">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.88671875" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="4" max="4" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="2">
+        <v>200000</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="E2" s="2">
+        <v>200000</v>
+      </c>
+      <c r="F2" s="2">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1500</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1000</v>
+      </c>
+      <c r="F3" s="2">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="2">
+        <v>5000</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="2">
+        <f>(B3)*(B4/100)*B5</f>
+        <v>500000</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="2">
+        <f>(B6-B2)/Ad_Spend</f>
+        <v>1.5</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+    </row>
+  </sheetData>
+  <scenarios current="2" sqref="B7">
+    <scenario name="Balanced" locked="1" count="2" user="Triveni" comment="Created by Triveni on 10-02-2026_x000a_Modified by Triveni on 10-02-2026">
+      <inputCells r="B2" val="200000"/>
+      <inputCells r="B3" val="1000"/>
+    </scenario>
+    <scenario name="Aggresive" locked="1" count="2" user="Triveni" comment="Created by Triveni on 10-02-2026_x000a_Modified by Triveni on 10-02-2026">
+      <inputCells r="B2" val="3000000"/>
+      <inputCells r="B3" val="1500"/>
+    </scenario>
+    <scenario name="Conservative" locked="1" count="2" user="Triveni" comment="Created by Triveni on 10-02-2026_x000a_Modified by Triveni on 10-02-2026">
+      <inputCells r="B2" val="100000"/>
+      <inputCells r="B3" val="600"/>
+    </scenario>
+  </scenarios>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BE379A-97F8-4417-8C8F-291C376599CC}">
   <dimension ref="A4:D14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1286,276 +1845,252 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D98FD759-83AD-4973-A6D0-DC90F1A1042F}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2">
-        <v>500</v>
-      </c>
-      <c r="D2" s="2">
-        <v>620</v>
-      </c>
-      <c r="E2" s="2">
-        <v>400</v>
-      </c>
-      <c r="F2" s="2">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2">
-        <v>100</v>
-      </c>
-      <c r="D3" s="2">
-        <v>250</v>
-      </c>
-      <c r="E3" s="2">
-        <v>90</v>
-      </c>
-      <c r="F3" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2">
-        <v>300</v>
-      </c>
-      <c r="D4" s="2">
-        <v>250</v>
-      </c>
-      <c r="E4" s="2">
-        <v>350</v>
-      </c>
-      <c r="F4" s="2">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2">
-        <v>10000</v>
-      </c>
-      <c r="D5" s="2">
-        <v>10000</v>
-      </c>
-      <c r="E5" s="2">
-        <v>10000</v>
-      </c>
-      <c r="F5" s="2">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2">
-        <f>(B2*B3)-(B4*B3+B5)</f>
-        <v>10000</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-  </sheetData>
-  <scenarios current="0" sqref="B6">
-    <scenario name="Expected" locked="1" count="4" user="Triveni" comment="Created by Triveni on 09-02-2026">
-      <inputCells r="B2" val="500"/>
-      <inputCells r="B3" val="100"/>
-      <inputCells r="B4" val="300"/>
-      <inputCells r="B5" val="10000"/>
-    </scenario>
-    <scenario name="Best_Case" locked="1" count="4" user="Triveni" comment="Created by Triveni on 09-02-2026">
-      <inputCells r="B2" val="620"/>
-      <inputCells r="B3" val="250"/>
-      <inputCells r="B4" val="250"/>
-      <inputCells r="B5" val="10000"/>
-    </scenario>
-    <scenario name="Worst_Case" locked="1" count="4" user="Triveni" comment="Created by Triveni on 09-02-2026">
-      <inputCells r="B2" val="400"/>
-      <inputCells r="B3" val="90"/>
-      <inputCells r="B4" val="350"/>
-      <inputCells r="B5" val="10000"/>
-    </scenario>
-  </scenarios>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89FEEC00-1B29-48B2-A252-2F127EEBDA47}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFCA57A5-308D-4116-A2EC-49927620C060}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="B2:G12"/>
+  <dimension ref="B2:G18"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="25.77734375" customWidth="1"/>
-    <col min="3" max="3" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="12.6640625" bestFit="1" customWidth="1" outlineLevel="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="17"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="2:7" ht="15.6" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="18" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" ht="43.2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>61</v>
+      <c r="E3" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" ht="21.6" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="G4" s="31" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="20"/>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
     </row>
     <row r="6" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="19"/>
-      <c r="C6" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="20">
-        <v>200000</v>
-      </c>
-      <c r="E6" s="23">
-        <v>200000</v>
-      </c>
-      <c r="F6" s="23">
-        <v>3000000</v>
-      </c>
-      <c r="G6" s="23">
-        <v>100000</v>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="32">
+        <v>12000</v>
+      </c>
+      <c r="E6" s="33">
+        <v>20000</v>
+      </c>
+      <c r="F6" s="33">
+        <v>10000</v>
+      </c>
+      <c r="G6" s="33">
+        <v>5000</v>
       </c>
     </row>
     <row r="7" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="19"/>
-      <c r="C7" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="20">
-        <v>1000</v>
-      </c>
-      <c r="E7" s="23">
-        <v>1000</v>
-      </c>
-      <c r="F7" s="23">
-        <v>1500</v>
-      </c>
-      <c r="G7" s="23">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B8" s="22" t="s">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="32">
+        <v>0.05</v>
+      </c>
+      <c r="E7" s="33">
+        <v>0.2</v>
+      </c>
+      <c r="F7" s="33">
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="33">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="18"/>
+      <c r="C8" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" s="32">
+        <v>7.5</v>
+      </c>
+      <c r="E8" s="33">
+        <v>0.1</v>
+      </c>
+      <c r="F8" s="33">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G8" s="33">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-    </row>
-    <row r="9" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="19"/>
-      <c r="C9" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="20">
-        <v>1.5</v>
-      </c>
-      <c r="E9" s="20">
-        <v>1.5</v>
-      </c>
-      <c r="F9" s="20">
-        <v>-0.75</v>
-      </c>
-      <c r="G9" s="20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="24" t="s">
+      <c r="C9" s="20"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+    </row>
+    <row r="10" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="30">
+        <v>10800</v>
+      </c>
+      <c r="E10" s="30">
+        <v>10800</v>
+      </c>
+      <c r="F10" s="30">
+        <v>10800</v>
+      </c>
+      <c r="G10" s="30">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" s="30">
+        <v>10773</v>
+      </c>
+      <c r="E11" s="30">
+        <v>12312</v>
+      </c>
+      <c r="F11" s="30">
+        <v>11286</v>
+      </c>
+      <c r="G11" s="30">
+        <v>10465.200000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="30">
+        <v>10650.8115</v>
+      </c>
+      <c r="E12" s="30">
+        <v>13911.263999999999</v>
+      </c>
+      <c r="F12" s="30">
+        <v>11689.325999999999</v>
+      </c>
+      <c r="G12" s="30">
+        <v>10050.88824</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="18"/>
+      <c r="C13" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="30">
+        <v>10416.145367249999</v>
+      </c>
+      <c r="E13" s="30">
+        <v>15548.298623999999</v>
+      </c>
+      <c r="F13" s="30">
+        <v>11976.148998000001</v>
+      </c>
+      <c r="G13" s="30">
+        <v>9548.5988924639896</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="18"/>
+      <c r="C14" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="30">
+        <v>10049.326449505899</v>
+      </c>
+      <c r="E14" s="30">
+        <v>17143.707262463999</v>
+      </c>
+      <c r="F14" s="30">
+        <v>12104.601563934</v>
+      </c>
+      <c r="G14" s="30">
+        <v>8949.1223391765907</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" s="34">
+        <v>35492.077761843699</v>
+      </c>
+      <c r="E15" s="34">
+        <v>45261.069682613997</v>
+      </c>
+      <c r="F15" s="34">
+        <v>38476.591715082403</v>
+      </c>
+      <c r="G15" s="34">
+        <v>33821.859058989299</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="24" t="s">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="24" t="s">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1564,152 +2099,334 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24145780-E5EB-4577-878A-05C93A422FE5}">
-  <dimension ref="A1:F7"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE06A407-BFD4-44E1-A13B-2777A813119D}">
+  <dimension ref="B1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.88671875" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" customWidth="1"/>
-    <col min="4" max="4" width="18.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" customWidth="1"/>
+    <col min="5" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="2">
-        <v>200000</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="2">
-        <v>3000000</v>
-      </c>
-      <c r="E2" s="2">
-        <v>200000</v>
-      </c>
-      <c r="F2" s="15">
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D3" s="2">
-        <v>1500</v>
-      </c>
-      <c r="E3" s="2">
-        <v>1000</v>
-      </c>
-      <c r="F3" s="15">
-        <v>6000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="2">
-        <v>10</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="2">
-        <v>5000</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+    <row r="1" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B1" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="23">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="23">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="23">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C4" s="23">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" s="23">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C6" s="23">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="23">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="23">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="24">
+        <v>1</v>
+      </c>
+      <c r="D10" s="25">
+        <v>2</v>
+      </c>
+      <c r="E10" s="25">
+        <v>3</v>
+      </c>
+      <c r="F10" s="24">
+        <v>4</v>
+      </c>
+      <c r="G10" s="25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="27">
+        <v>12000</v>
+      </c>
+      <c r="D11" s="26">
+        <f>C11*(1+$C$3)</f>
+        <v>12600</v>
+      </c>
+      <c r="E11" s="26">
+        <f t="shared" ref="E11:G11" si="0">D11*(1+$C$3)</f>
+        <v>13230</v>
+      </c>
+      <c r="F11" s="26">
+        <f t="shared" si="0"/>
+        <v>13891.5</v>
+      </c>
+      <c r="G11" s="26">
+        <f t="shared" si="0"/>
+        <v>14586.075000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="26">
+        <v>7.5</v>
+      </c>
+      <c r="D12" s="26">
+        <f>C12*(1+$C$8)</f>
+        <v>7.7250000000000005</v>
+      </c>
+      <c r="E12" s="26">
+        <f t="shared" ref="E12:G12" si="1">D12*(1+$C$8)</f>
+        <v>7.9567500000000004</v>
+      </c>
+      <c r="F12" s="26">
+        <f t="shared" si="1"/>
+        <v>8.1954525</v>
+      </c>
+      <c r="G12" s="26">
+        <f t="shared" si="1"/>
+        <v>8.4413160749999996</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="26">
+        <v>6</v>
+      </c>
+      <c r="D13" s="26">
+        <f>C13*(1+$C$7)</f>
+        <v>6.3000000000000007</v>
+      </c>
+      <c r="E13" s="26">
+        <f t="shared" ref="E13:G13" si="2">D13*(1+$C$7)</f>
+        <v>6.6150000000000011</v>
+      </c>
+      <c r="F13" s="26">
+        <f t="shared" si="2"/>
+        <v>6.9457500000000012</v>
+      </c>
+      <c r="G13" s="26">
+        <f t="shared" si="2"/>
+        <v>7.2930375000000014</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="2">
-        <f>(B3)*(B4/100)*B5</f>
-        <v>500000</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="2">
-        <f>(B6-B2)/Ad_Spend</f>
-        <v>1.5</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
+      <c r="C14" s="26">
+        <f>C11*C12</f>
+        <v>90000</v>
+      </c>
+      <c r="D14" s="26">
+        <f t="shared" ref="D14:G14" si="3">D11*D12</f>
+        <v>97335</v>
+      </c>
+      <c r="E14" s="26">
+        <f t="shared" si="3"/>
+        <v>105267.80250000001</v>
+      </c>
+      <c r="F14" s="26">
+        <f t="shared" si="3"/>
+        <v>113847.12840375</v>
+      </c>
+      <c r="G14" s="26">
+        <f t="shared" si="3"/>
+        <v>123125.66936865562</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" s="26">
+        <f>C11*C13</f>
+        <v>72000</v>
+      </c>
+      <c r="D15" s="26">
+        <f t="shared" ref="D15:G15" si="4">D11*D13</f>
+        <v>79380.000000000015</v>
+      </c>
+      <c r="E15" s="26">
+        <f t="shared" si="4"/>
+        <v>87516.450000000012</v>
+      </c>
+      <c r="F15" s="26">
+        <f t="shared" si="4"/>
+        <v>96486.886125000019</v>
+      </c>
+      <c r="G15" s="26">
+        <f t="shared" si="4"/>
+        <v>106376.79195281252</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="26">
+        <f>C14-C15</f>
+        <v>18000</v>
+      </c>
+      <c r="D16" s="26">
+        <f t="shared" ref="D16:G16" si="5">D14-D15</f>
+        <v>17954.999999999985</v>
+      </c>
+      <c r="E16" s="26">
+        <f t="shared" si="5"/>
+        <v>17751.352499999994</v>
+      </c>
+      <c r="F16" s="26">
+        <f t="shared" si="5"/>
+        <v>17360.242278749982</v>
+      </c>
+      <c r="G16" s="26">
+        <f t="shared" si="5"/>
+        <v>16748.877415843104</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="26">
+        <f>C16*$C$1</f>
+        <v>7200</v>
+      </c>
+      <c r="D17" s="26">
+        <f t="shared" ref="D17:G17" si="6">D16*$C$1</f>
+        <v>7181.9999999999945</v>
+      </c>
+      <c r="E17" s="26">
+        <f t="shared" si="6"/>
+        <v>7100.5409999999974</v>
+      </c>
+      <c r="F17" s="26">
+        <f t="shared" si="6"/>
+        <v>6944.0969114999934</v>
+      </c>
+      <c r="G17" s="26">
+        <f t="shared" si="6"/>
+        <v>6699.5509663372422</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="28">
+        <f>C16-C17</f>
+        <v>10800</v>
+      </c>
+      <c r="D18" s="28">
+        <f t="shared" ref="D18:G18" si="7">D16-D17</f>
+        <v>10772.999999999991</v>
+      </c>
+      <c r="E18" s="28">
+        <f t="shared" si="7"/>
+        <v>10650.811499999996</v>
+      </c>
+      <c r="F18" s="28">
+        <f t="shared" si="7"/>
+        <v>10416.145367249988</v>
+      </c>
+      <c r="G18" s="28">
+        <f t="shared" si="7"/>
+        <v>10049.326449505861</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" s="29">
+        <f>NPV(Interest_Rate,C18:G18)</f>
+        <v>35492.07776184375</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C23" t="str">
+        <f ca="1">_xlfn.FORMULATEXT(C20)</f>
+        <v>=NPV(Interest_Rate,C18:G18)</v>
+      </c>
     </row>
   </sheetData>
-  <scenarios current="2" sqref="B7">
-    <scenario name="Balanced" locked="1" count="2" user="Triveni" comment="Created by Triveni on 10-02-2026_x000a_Modified by Triveni on 10-02-2026">
-      <inputCells r="B2" val="200000"/>
-      <inputCells r="B3" val="1000"/>
+  <scenarios current="0" sqref="C18:G18 C20">
+    <scenario name="Best" locked="1" count="3" user="Triveni" comment="Created by Triveni on 29-03-2026">
+      <inputCells r="C2" val="20000" numFmtId="2"/>
+      <inputCells r="C3" val="0.2" numFmtId="2"/>
+      <inputCells r="C4" val="0.1" numFmtId="2"/>
     </scenario>
-    <scenario name="Aggresive" locked="1" count="2" user="Triveni" comment="Created by Triveni on 10-02-2026_x000a_Modified by Triveni on 10-02-2026">
-      <inputCells r="B2" val="3000000"/>
-      <inputCells r="B3" val="1500"/>
+    <scenario name="Most Probably" locked="1" count="3" user="Triveni" comment="Created by Triveni on 29-03-2026">
+      <inputCells r="C2" val="10000" numFmtId="2"/>
+      <inputCells r="C3" val="0.1" numFmtId="2"/>
+      <inputCells r="C4" val="0.075" numFmtId="2"/>
     </scenario>
-    <scenario name="Conservative" locked="1" count="2" user="Triveni" comment="Created by Triveni on 10-02-2026_x000a_Modified by Triveni on 10-02-2026">
-      <inputCells r="B2" val="100000"/>
-      <inputCells r="B3" val="600"/>
+    <scenario name="Worst" locked="1" count="3" user="Triveni" comment="Created by Triveni on 29-03-2026">
+      <inputCells r="C2" val="5000" numFmtId="2"/>
+      <inputCells r="C3" val="0.02" numFmtId="2"/>
+      <inputCells r="C4" val="0.05" numFmtId="2"/>
     </scenario>
   </scenarios>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="C17 D17:G17" formula="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>